--- a/template/postcard_story.xlsx
+++ b/template/postcard_story.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$211</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="663">
   <si>
     <t>id</t>
   </si>
@@ -3855,6 +3855,67 @@
 祝你今天愉快。
 朱塞佩</t>
   </si>
+  <si>
+    <t>DE-16306788</t>
+  </si>
+  <si>
+    <t>Hello, many greetings from the North of Germany. By NORBERT.Near HAMBURG Happy Postcrossing.</t>
+  </si>
+  <si>
+    <t>您好，来自德国北部的问候。诺伯特（汉堡附近）祝您邮递愉快！</t>
+  </si>
+  <si>
+    <t>FR-1867589</t>
+  </si>
+  <si>
+    <t>Hello Arthur! I'm a bit late to send you my post coming, Sorry! In French we say "Mieux, je t'aime" que jamais. Hope Xiaoxiao will like the post! Best Regards Claudia</t>
+  </si>
+  <si>
+    <t>你好，亚瑟！我发邮件晚了，抱歉！法语里我们会说“Mieux, je t'aime” que jamais。希望小小会喜欢这篇帖子！祝好，克劳迪娅</t>
+  </si>
+  <si>
+    <t>KR-386201</t>
+  </si>
+  <si>
+    <t>새해 복 많이 받으세요!
+Happy New Year!
+I haven't set my goals for this year yet, and Jan. 1st has already passed, so I am waiting for Feb. 17th (Lunar New Year). What is your goal in 2026?
+2026 JAN 29
+CINA
+2026 병오년, 붉은 말의 해 Red Horse Year.</t>
+  </si>
+  <si>
+    <t>새해 복 많이 받으세요(新年快乐！)
+祝新的一年幸福满满！
+我还没有设定今年的目标，而1月1日已经过去了，所以我在等待2月17日（农历新年）。你的2026年目标是什么？
+2026年1月29日
+中国
+2026年丙午年，红马年。</t>
+  </si>
+  <si>
+    <t>DE-16304639</t>
+  </si>
+  <si>
+    <t>Hello Arthur,
+best wishes from the east of Germany.
+My name is Jennifer
+and I'm 26 years old. We
+got a lot of snow in the
+last couple days here. How's
+the weather at your
+place? Best wishes,
+Jennifer</t>
+  </si>
+  <si>
+    <t>你好，Arthur，
+来自德国东部的良好祝愿。
+我的名字是Jennifer，
+我26岁了。我们这里
+过去几天降了很多雪。
+你那里天气如何？
+祝好，
+Jennifer</t>
+  </si>
 </sst>
 </file>
 
@@ -4033,18 +4094,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Segoe UI Symbol"/>
       <charset val="134"/>
     </font>
@@ -4063,8 +4112,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="204"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4074,8 +4123,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Cambria"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -4901,7 +4962,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E211"/>
+  <dimension ref="A1:E215"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="19.25" style="1" customWidth="1"/>
@@ -7258,7 +7319,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="209" ht="216" spans="1:3">
+    <row r="209" ht="158.4" spans="1:3">
       <c r="A209" s="1" t="s">
         <v>641</v>
       </c>
@@ -7283,7 +7344,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="211" ht="100.8" spans="1:3">
+    <row r="211" ht="72" spans="1:3">
       <c r="A211" s="1" t="s">
         <v>648</v>
       </c>
@@ -7294,8 +7355,52 @@
         <v>650</v>
       </c>
     </row>
+    <row r="212" ht="28.8" spans="1:3">
+      <c r="A212" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="213" ht="57.6" spans="1:3">
+      <c r="A213" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="214" ht="115.2" spans="1:3">
+      <c r="A214" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="215" ht="129.6" spans="1:3">
+      <c r="A215" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E210" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E211" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="1">
       <filters>
         <filter val="Hello, Arthur&#10;Your daughter is adorable! I hope she enjoys the bunnies. I hope you reach your goal of 100 rides. I haven't ridden a bike in at least 10 years, I miss it!&#10;&#10;- Olivia"/>

--- a/template/postcard_story.xlsx
+++ b/template/postcard_story.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$215</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3868,10 +3868,10 @@
     <t>FR-1867589</t>
   </si>
   <si>
-    <t>Hello Arthur! I'm a bit late to send you my post coming, Sorry! In French we say "Mieux, je t'aime" que jamais. Hope Xiaoxiao will like the post! Best Regards Claudia</t>
-  </si>
-  <si>
-    <t>你好，亚瑟！我发邮件晚了，抱歉！法语里我们会说“Mieux, je t'aime” que jamais。希望小小会喜欢这篇帖子！祝好，克劳迪娅</t>
+    <t>Hello Arthur! I'm a bit late to send you my post coming, Sorry! In French we say "Mieux vaut tard que jamais". Hope Xiaoxiao will like the post! Best Regards Claudia</t>
+  </si>
+  <si>
+    <t>你好，亚瑟！我发邮件晚了，抱歉！法语里我们会说“Mieux vaut tard que jamais”（“迟到总比不到好”）。希望笑笑会喜欢这篇帖子！祝好，克劳迪娅</t>
   </si>
   <si>
     <t>KR-386201</t>
@@ -4093,20 +4093,32 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Cambria"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI Symbol"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI Emoji"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4123,20 +4135,8 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Cambria"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
+      <name val="Segoe UI Emoji"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -7400,7 +7400,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E211" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E215" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="1">
       <filters>
         <filter val="Hello, Arthur&#10;Your daughter is adorable! I hope she enjoys the bunnies. I hope you reach your goal of 100 rides. I haven't ridden a bike in at least 10 years, I miss it!&#10;&#10;- Olivia"/>

--- a/template/postcard_story.xlsx
+++ b/template/postcard_story.xlsx
@@ -2606,11 +2606,15 @@
   </si>
   <si>
     <t>Hello Siyuan,
-Kind regards from the north-east of Germany. I live in a small village just by the bay between Berlin and the Baltic Sea. This tower was built as a XXX co.100 years ago to provide all houses with fresh water. Today, it is empty and became the symbol of our village. Happy postcrossing, Lupe</t>
-  </si>
-  <si>
-    <t>你好，Siyuan，
-来自德国东北部的问候。我住在柏林和波罗的海之间的一个小村庄里。这座塔是 100 年前由 XXX 公司建造的，为所有房屋提供淡水。今天，它空了，成为了我们村庄的象征。祝你过个愉快的明信片，Lupe</t>
+Kind regards from the north-east of Germany. I live in a small village just by the bay between Berlin and the Baltic Sea. This tower was built as a reservoir ca.100 years ago to provide all houses with fresh water. Today, it is empty and became the symbol of our village. 
+Happy postcrossing
+Lutz</t>
+  </si>
+  <si>
+    <t>你好，思远：
+向你致以来自德国东北部的亲切问候。我住在一个位于柏林和波罗的海正中间的小村庄里。这座塔大约建于100年前，最初是作为蓄水池为家家户户提供淡水的。如今它虽然已经空置，但已成为我们村庄的象征。
+祝明信片交换愉快！
+Lutz</t>
   </si>
   <si>
     <t>DE-15094225</t>
@@ -4106,13 +4110,19 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="204"/>
+      <name val="Segoe UI Emoji"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI Symbol"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI Emoji"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4130,14 +4140,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Segoe UI Emoji"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI Emoji"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="33">
@@ -4959,7 +4963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E215"/>
@@ -4988,7 +4992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="2" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -4999,7 +5003,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="3" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -5010,7 +5014,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="4" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
@@ -5021,7 +5025,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="5" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -5032,7 +5036,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="94.15" hidden="1" customHeight="1" spans="1:3">
+    <row r="6" s="1" customFormat="1" ht="94.15" customHeight="1" spans="1:3">
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
@@ -5043,7 +5047,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="7" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A7" s="3" t="s">
         <v>20</v>
       </c>
@@ -5054,7 +5058,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="8" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A8" s="3" t="s">
         <v>23</v>
       </c>
@@ -5065,7 +5069,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="9" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
@@ -5076,7 +5080,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="10" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A10" s="3" t="s">
         <v>29</v>
       </c>
@@ -5087,7 +5091,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="11" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A11" s="3" t="s">
         <v>32</v>
       </c>
@@ -5098,7 +5102,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="12" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A12" s="3" t="s">
         <v>35</v>
       </c>
@@ -5109,7 +5113,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="13" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
@@ -5120,7 +5124,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="14" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A14" s="3" t="s">
         <v>41</v>
       </c>
@@ -5131,7 +5135,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="15" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A15" s="3" t="s">
         <v>44</v>
       </c>
@@ -5142,7 +5146,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="16" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A16" s="3" t="s">
         <v>47</v>
       </c>
@@ -5170,7 +5174,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="18" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A18" s="3" t="s">
         <v>55</v>
       </c>
@@ -5181,7 +5185,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="19" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A19" s="3" t="s">
         <v>58</v>
       </c>
@@ -5192,7 +5196,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="20" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A20" s="3" t="s">
         <v>61</v>
       </c>
@@ -5220,7 +5224,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="22" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A22" s="3" t="s">
         <v>69</v>
       </c>
@@ -5231,7 +5235,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="23" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A23" s="3" t="s">
         <v>72</v>
       </c>
@@ -5242,7 +5246,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="24" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A24" s="3" t="s">
         <v>75</v>
       </c>
@@ -5253,7 +5257,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="25" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A25" s="3" t="s">
         <v>78</v>
       </c>
@@ -5281,7 +5285,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="58.15" hidden="1" customHeight="1" spans="1:3">
+    <row r="27" s="1" customFormat="1" ht="58.15" customHeight="1" spans="1:3">
       <c r="A27" s="3" t="s">
         <v>86</v>
       </c>
@@ -5292,7 +5296,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="28" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A28" s="3" t="s">
         <v>89</v>
       </c>
@@ -5303,7 +5307,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="29" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A29" s="3" t="s">
         <v>92</v>
       </c>
@@ -5314,7 +5318,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="153.75" hidden="1" customHeight="1" spans="1:3">
+    <row r="30" s="1" customFormat="1" ht="153.75" customHeight="1" spans="1:3">
       <c r="A30" s="3" t="s">
         <v>95</v>
       </c>
@@ -5325,7 +5329,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="31" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A31" s="3" t="s">
         <v>98</v>
       </c>
@@ -5336,7 +5340,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="32" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A32" s="3" t="s">
         <v>101</v>
       </c>
@@ -5347,7 +5351,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="33" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A33" s="3" t="s">
         <v>104</v>
       </c>
@@ -5358,7 +5362,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="34" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A34" s="3" t="s">
         <v>107</v>
       </c>
@@ -5369,7 +5373,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="35" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A35" s="3" t="s">
         <v>110</v>
       </c>
@@ -5380,7 +5384,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="36" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A36" s="3" t="s">
         <v>113</v>
       </c>
@@ -5391,7 +5395,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="37" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A37" s="3" t="s">
         <v>116</v>
       </c>
@@ -5402,7 +5406,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="38" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A38" s="3" t="s">
         <v>119</v>
       </c>
@@ -5413,7 +5417,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="39" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A39" s="3" t="s">
         <v>122</v>
       </c>
@@ -5424,7 +5428,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="40" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A40" s="3" t="s">
         <v>125</v>
       </c>
@@ -5435,7 +5439,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="41" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A41" s="3" t="s">
         <v>128</v>
       </c>
@@ -5446,7 +5450,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="42" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A42" s="3" t="s">
         <v>131</v>
       </c>
@@ -5457,7 +5461,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="43" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A43" s="3" t="s">
         <v>134</v>
       </c>
@@ -5468,7 +5472,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="44" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A44" s="3" t="s">
         <v>137</v>
       </c>
@@ -5479,7 +5483,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="45" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A45" s="3" t="s">
         <v>140</v>
       </c>
@@ -5490,7 +5494,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="46" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A46" s="3" t="s">
         <v>143</v>
       </c>
@@ -5501,7 +5505,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="47" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A47" s="3" t="s">
         <v>146</v>
       </c>
@@ -5512,7 +5516,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="48" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A48" s="3" t="s">
         <v>149</v>
       </c>
@@ -5523,7 +5527,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" ht="18.4" hidden="1" customHeight="1" spans="1:3">
+    <row r="49" s="1" customFormat="1" ht="18.4" customHeight="1" spans="1:3">
       <c r="A49" s="3" t="s">
         <v>152</v>
       </c>
@@ -5534,7 +5538,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="50" ht="18.75" hidden="1" customHeight="1" spans="1:3">
+    <row r="50" ht="18.75" customHeight="1" spans="1:3">
       <c r="A50" s="3" t="s">
         <v>155</v>
       </c>
@@ -5545,7 +5549,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="51" ht="18.75" hidden="1" customHeight="1" spans="1:3">
+    <row r="51" ht="18.75" customHeight="1" spans="1:3">
       <c r="A51" s="1" t="s">
         <v>158</v>
       </c>
@@ -5556,7 +5560,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" ht="84" hidden="1" customHeight="1" spans="1:3">
+    <row r="52" s="1" customFormat="1" ht="84" customHeight="1" spans="1:3">
       <c r="A52" s="3" t="s">
         <v>161</v>
       </c>
@@ -5567,7 +5571,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="53" ht="72" hidden="1" spans="1:3">
+    <row r="53" ht="72" spans="1:3">
       <c r="A53" s="1" t="s">
         <v>164</v>
       </c>
@@ -5578,7 +5582,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="54" ht="100.8" hidden="1" spans="1:3">
+    <row r="54" ht="100.8" spans="1:3">
       <c r="A54" s="1" t="s">
         <v>167</v>
       </c>
@@ -5589,7 +5593,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="55" ht="115.2" hidden="1" spans="1:3">
+    <row r="55" ht="115.2" spans="1:3">
       <c r="A55" s="1" t="s">
         <v>170</v>
       </c>
@@ -5600,7 +5604,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="56" ht="72" hidden="1" spans="1:3">
+    <row r="56" ht="72" spans="1:3">
       <c r="A56" s="1" t="s">
         <v>173</v>
       </c>
@@ -5611,7 +5615,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="57" ht="100.8" hidden="1" spans="1:3">
+    <row r="57" ht="100.8" spans="1:3">
       <c r="A57" s="1" t="s">
         <v>176</v>
       </c>
@@ -5622,7 +5626,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="58" ht="72" hidden="1" spans="1:3">
+    <row r="58" ht="72" spans="1:3">
       <c r="A58" s="1" t="s">
         <v>179</v>
       </c>
@@ -5633,7 +5637,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="59" ht="360" hidden="1" spans="1:3">
+    <row r="59" ht="360" spans="1:3">
       <c r="A59" s="1" t="s">
         <v>182</v>
       </c>
@@ -5644,7 +5648,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="60" ht="172.8" hidden="1" spans="1:3">
+    <row r="60" ht="172.8" spans="1:3">
       <c r="A60" s="1" t="s">
         <v>185</v>
       </c>
@@ -5655,7 +5659,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="61" ht="72" hidden="1" spans="1:3">
+    <row r="61" ht="72" spans="1:3">
       <c r="A61" s="1" t="s">
         <v>188</v>
       </c>
@@ -5666,7 +5670,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="62" ht="100.8" hidden="1" spans="1:3">
+    <row r="62" ht="100.8" spans="1:3">
       <c r="A62" s="1" t="s">
         <v>191</v>
       </c>
@@ -5677,7 +5681,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="63" ht="129.6" hidden="1" spans="1:3">
+    <row r="63" ht="129.6" spans="1:3">
       <c r="A63" s="1" t="s">
         <v>194</v>
       </c>
@@ -5688,7 +5692,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="64" ht="144" hidden="1" spans="1:3">
+    <row r="64" ht="144" spans="1:3">
       <c r="A64" s="1" t="s">
         <v>197</v>
       </c>
@@ -5699,7 +5703,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="65" ht="57.6" hidden="1" spans="1:3">
+    <row r="65" ht="57.6" spans="1:3">
       <c r="A65" s="1" t="s">
         <v>200</v>
       </c>
@@ -5727,7 +5731,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="67" ht="129.6" hidden="1" spans="1:3">
+    <row r="67" ht="129.6" spans="1:3">
       <c r="A67" s="1" t="s">
         <v>208</v>
       </c>
@@ -5738,7 +5742,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="68" ht="100.8" hidden="1" spans="1:3">
+    <row r="68" ht="100.8" spans="1:3">
       <c r="A68" s="1" t="s">
         <v>210</v>
       </c>
@@ -5749,7 +5753,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="69" ht="158.4" hidden="1" spans="1:3">
+    <row r="69" ht="158.4" spans="1:3">
       <c r="A69" s="1" t="s">
         <v>213</v>
       </c>
@@ -5760,7 +5764,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="70" ht="57.6" hidden="1" spans="1:3">
+    <row r="70" ht="57.6" spans="1:3">
       <c r="A70" s="1" t="s">
         <v>216</v>
       </c>
@@ -5771,7 +5775,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="71" ht="43.2" hidden="1" spans="1:3">
+    <row r="71" ht="43.2" spans="1:3">
       <c r="A71" s="1" t="s">
         <v>219</v>
       </c>
@@ -5782,7 +5786,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="72" ht="100.8" hidden="1" spans="1:3">
+    <row r="72" ht="100.8" spans="1:3">
       <c r="A72" s="1" t="s">
         <v>222</v>
       </c>
@@ -5793,7 +5797,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="73" ht="100.8" hidden="1" spans="1:3">
+    <row r="73" ht="100.8" spans="1:3">
       <c r="A73" s="1" t="s">
         <v>225</v>
       </c>
@@ -5804,7 +5808,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="74" ht="72" hidden="1" spans="1:3">
+    <row r="74" ht="72" spans="1:3">
       <c r="A74" s="1" t="s">
         <v>228</v>
       </c>
@@ -5815,7 +5819,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" ht="72" hidden="1" spans="1:3">
+    <row r="75" ht="72" spans="1:3">
       <c r="A75" s="1" t="s">
         <v>231</v>
       </c>
@@ -5826,7 +5830,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="76" ht="43.2" hidden="1" spans="1:3">
+    <row r="76" ht="43.2" spans="1:3">
       <c r="A76" s="1" t="s">
         <v>234</v>
       </c>
@@ -5837,7 +5841,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="77" ht="28.8" hidden="1" spans="1:3">
+    <row r="77" ht="28.8" spans="1:3">
       <c r="A77" s="1" t="s">
         <v>237</v>
       </c>
@@ -5848,7 +5852,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="78" ht="230.4" hidden="1" spans="1:3">
+    <row r="78" ht="230.4" spans="1:3">
       <c r="A78" s="1" t="s">
         <v>240</v>
       </c>
@@ -5859,7 +5863,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="79" ht="57.6" hidden="1" spans="1:3">
+    <row r="79" ht="57.6" spans="1:3">
       <c r="A79" s="1" t="s">
         <v>243</v>
       </c>
@@ -5870,7 +5874,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="80" ht="100.8" hidden="1" spans="1:3">
+    <row r="80" ht="100.8" spans="1:3">
       <c r="A80" s="1" t="s">
         <v>246</v>
       </c>
@@ -5881,7 +5885,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="81" ht="72" hidden="1" spans="1:3">
+    <row r="81" ht="72" spans="1:3">
       <c r="A81" s="1" t="s">
         <v>249</v>
       </c>
@@ -5892,7 +5896,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="82" ht="158.4" hidden="1" spans="1:3">
+    <row r="82" ht="158.4" spans="1:3">
       <c r="A82" s="1" t="s">
         <v>252</v>
       </c>
@@ -5903,7 +5907,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="83" ht="28.8" hidden="1" spans="1:3">
+    <row r="83" ht="28.8" spans="1:3">
       <c r="A83" s="1" t="s">
         <v>255</v>
       </c>
@@ -5931,7 +5935,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="85" ht="374.4" hidden="1" spans="1:3">
+    <row r="85" ht="374.4" spans="1:3">
       <c r="A85" s="1" t="s">
         <v>263</v>
       </c>
@@ -5942,7 +5946,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="86" ht="115.2" hidden="1" spans="1:3">
+    <row r="86" ht="115.2" spans="1:3">
       <c r="A86" s="1" t="s">
         <v>266</v>
       </c>
@@ -5953,7 +5957,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="87" ht="57.6" hidden="1" spans="1:3">
+    <row r="87" ht="57.6" spans="1:3">
       <c r="A87" s="1" t="s">
         <v>269</v>
       </c>
@@ -5964,7 +5968,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="88" ht="86.4" hidden="1" spans="1:3">
+    <row r="88" ht="86.4" spans="1:3">
       <c r="A88" s="1" t="s">
         <v>272</v>
       </c>
@@ -5975,7 +5979,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="89" ht="57.6" hidden="1" spans="1:3">
+    <row r="89" ht="57.6" spans="1:3">
       <c r="A89" s="1" t="s">
         <v>275</v>
       </c>
@@ -5986,7 +5990,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="90" ht="115.2" hidden="1" spans="1:3">
+    <row r="90" ht="115.2" spans="1:3">
       <c r="A90" s="7" t="s">
         <v>278</v>
       </c>
@@ -5997,7 +6001,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="91" ht="115.2" hidden="1" spans="1:3">
+    <row r="91" ht="115.2" spans="1:3">
       <c r="A91" s="7" t="s">
         <v>281</v>
       </c>
@@ -6008,7 +6012,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="92" ht="86.4" hidden="1" spans="1:3">
+    <row r="92" ht="86.4" spans="1:3">
       <c r="A92" s="7" t="s">
         <v>284</v>
       </c>
@@ -6019,7 +6023,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="93" ht="86.4" hidden="1" spans="1:3">
+    <row r="93" ht="86.4" spans="1:3">
       <c r="A93" s="7" t="s">
         <v>287</v>
       </c>
@@ -6030,7 +6034,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="94" ht="103.2" hidden="1" spans="1:3">
+    <row r="94" ht="103.2" spans="1:3">
       <c r="A94" s="7" t="s">
         <v>290</v>
       </c>
@@ -6041,7 +6045,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="95" ht="86.4" hidden="1" spans="1:3">
+    <row r="95" ht="86.4" spans="1:3">
       <c r="A95" s="7" t="s">
         <v>293</v>
       </c>
@@ -6052,7 +6056,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="96" ht="100.8" hidden="1" spans="1:3">
+    <row r="96" ht="100.8" spans="1:3">
       <c r="A96" s="7" t="s">
         <v>296</v>
       </c>
@@ -6063,7 +6067,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="97" ht="57.6" hidden="1" spans="1:3">
+    <row r="97" ht="57.6" spans="1:3">
       <c r="A97" s="7" t="s">
         <v>299</v>
       </c>
@@ -6074,7 +6078,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="98" ht="72" hidden="1" spans="1:3">
+    <row r="98" ht="72" spans="1:3">
       <c r="A98" s="7" t="s">
         <v>302</v>
       </c>
@@ -6085,7 +6089,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="99" ht="86.4" hidden="1" spans="1:3">
+    <row r="99" ht="86.4" spans="1:3">
       <c r="A99" s="7" t="s">
         <v>305</v>
       </c>
@@ -6096,7 +6100,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="100" ht="102" hidden="1" spans="1:3">
+    <row r="100" ht="102" spans="1:3">
       <c r="A100" s="7" t="s">
         <v>308</v>
       </c>
@@ -6107,7 +6111,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="101" ht="100.8" hidden="1" spans="1:3">
+    <row r="101" ht="100.8" spans="1:3">
       <c r="A101" s="7" t="s">
         <v>311</v>
       </c>
@@ -6118,7 +6122,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="102" ht="72" hidden="1" spans="1:3">
+    <row r="102" ht="72" spans="1:3">
       <c r="A102" s="7" t="s">
         <v>314</v>
       </c>
@@ -6129,7 +6133,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="103" ht="43.2" hidden="1" spans="1:3">
+    <row r="103" ht="43.2" spans="1:3">
       <c r="A103" s="7" t="s">
         <v>317</v>
       </c>
@@ -6140,7 +6144,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="104" ht="57.6" hidden="1" spans="1:3">
+    <row r="104" ht="57.6" spans="1:3">
       <c r="A104" s="7" t="s">
         <v>320</v>
       </c>
@@ -6151,7 +6155,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="105" ht="86.4" hidden="1" spans="1:3">
+    <row r="105" ht="86.4" spans="1:3">
       <c r="A105" s="7" t="s">
         <v>323</v>
       </c>
@@ -6162,7 +6166,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="106" ht="28.8" hidden="1" spans="1:3">
+    <row r="106" ht="28.8" spans="1:3">
       <c r="A106" s="7" t="s">
         <v>326</v>
       </c>
@@ -6173,7 +6177,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="107" ht="72" hidden="1" spans="1:3">
+    <row r="107" ht="72" spans="1:3">
       <c r="A107" s="7" t="s">
         <v>329</v>
       </c>
@@ -6201,7 +6205,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="109" ht="100.8" hidden="1" spans="1:3">
+    <row r="109" ht="100.8" spans="1:3">
       <c r="A109" s="7" t="s">
         <v>337</v>
       </c>
@@ -6212,7 +6216,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="110" ht="28.8" hidden="1" spans="1:3">
+    <row r="110" ht="28.8" spans="1:3">
       <c r="A110" s="7" t="s">
         <v>340</v>
       </c>
@@ -6223,7 +6227,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="111" ht="57.6" hidden="1" spans="1:3">
+    <row r="111" ht="57.6" spans="1:3">
       <c r="A111" s="7" t="s">
         <v>342</v>
       </c>
@@ -6234,7 +6238,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="112" ht="100.8" hidden="1" spans="1:3">
+    <row r="112" ht="100.8" spans="1:3">
       <c r="A112" s="7" t="s">
         <v>345</v>
       </c>
@@ -6245,7 +6249,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="113" ht="86.4" hidden="1" spans="1:3">
+    <row r="113" ht="86.4" spans="1:3">
       <c r="A113" s="7" t="s">
         <v>348</v>
       </c>
@@ -6256,7 +6260,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="114" ht="43.2" hidden="1" spans="1:3">
+    <row r="114" ht="43.2" spans="1:3">
       <c r="A114" s="1" t="s">
         <v>351</v>
       </c>
@@ -6267,7 +6271,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="115" ht="86.4" hidden="1" spans="1:3">
+    <row r="115" ht="86.4" spans="1:3">
       <c r="A115" s="1" t="s">
         <v>354</v>
       </c>
@@ -6278,7 +6282,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="116" ht="86.4" hidden="1" spans="1:3">
+    <row r="116" ht="86.4" spans="1:3">
       <c r="A116" s="1" t="s">
         <v>357</v>
       </c>
@@ -6289,7 +6293,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="117" ht="115.2" hidden="1" spans="1:3">
+    <row r="117" ht="115.2" spans="1:3">
       <c r="A117" s="1" t="s">
         <v>360</v>
       </c>
@@ -6300,7 +6304,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="118" ht="100.8" hidden="1" spans="1:3">
+    <row r="118" ht="100.8" spans="1:3">
       <c r="A118" s="1" t="s">
         <v>362</v>
       </c>
@@ -6311,7 +6315,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="119" ht="201.6" hidden="1" spans="1:3">
+    <row r="119" ht="201.6" spans="1:3">
       <c r="A119" s="1" t="s">
         <v>365</v>
       </c>
@@ -6322,7 +6326,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="120" ht="129.6" hidden="1" spans="1:3">
+    <row r="120" ht="129.6" spans="1:3">
       <c r="A120" s="1" t="s">
         <v>368</v>
       </c>
@@ -6333,7 +6337,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="121" ht="57.6" hidden="1" spans="1:3">
+    <row r="121" ht="57.6" spans="1:3">
       <c r="A121" s="1" t="s">
         <v>371</v>
       </c>
@@ -6344,7 +6348,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="122" ht="100.8" hidden="1" spans="1:3">
+    <row r="122" ht="100.8" spans="1:3">
       <c r="A122" s="1" t="s">
         <v>374</v>
       </c>
@@ -6355,7 +6359,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="123" ht="100.8" hidden="1" spans="1:3">
+    <row r="123" ht="100.8" spans="1:3">
       <c r="A123" s="1" t="s">
         <v>377</v>
       </c>
@@ -6383,7 +6387,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="125" ht="144" hidden="1" spans="1:3">
+    <row r="125" ht="144" spans="1:3">
       <c r="A125" s="7" t="s">
         <v>385</v>
       </c>
@@ -6394,7 +6398,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="126" ht="100.8" hidden="1" spans="1:3">
+    <row r="126" ht="100.8" spans="1:3">
       <c r="A126" s="1" t="s">
         <v>388</v>
       </c>
@@ -6405,7 +6409,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="127" ht="129.6" hidden="1" spans="1:3">
+    <row r="127" ht="129.6" spans="1:3">
       <c r="A127" s="1" t="s">
         <v>391</v>
       </c>
@@ -6416,7 +6420,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="128" ht="57.6" hidden="1" spans="1:3">
+    <row r="128" ht="57.6" spans="1:3">
       <c r="A128" s="1" t="s">
         <v>394</v>
       </c>
@@ -6427,7 +6431,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="129" ht="100.8" hidden="1" spans="1:3">
+    <row r="129" ht="100.8" spans="1:3">
       <c r="A129" s="1" t="s">
         <v>397</v>
       </c>
@@ -6438,7 +6442,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="130" ht="72" hidden="1" spans="1:3">
+    <row r="130" ht="72" spans="1:3">
       <c r="A130" s="1" t="s">
         <v>400</v>
       </c>
@@ -6449,7 +6453,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="131" ht="115.2" hidden="1" spans="1:3">
+    <row r="131" ht="115.2" spans="1:3">
       <c r="A131" s="1" t="s">
         <v>403</v>
       </c>
@@ -6460,7 +6464,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="132" ht="115.2" hidden="1" spans="1:3">
+    <row r="132" ht="115.2" spans="1:3">
       <c r="A132" s="1" t="s">
         <v>406</v>
       </c>
@@ -6471,7 +6475,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="133" ht="86.4" hidden="1" spans="1:3">
+    <row r="133" ht="86.4" spans="1:3">
       <c r="A133" s="1" t="s">
         <v>409</v>
       </c>
@@ -6482,7 +6486,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="134" ht="100.8" hidden="1" spans="1:3">
+    <row r="134" ht="100.8" spans="1:3">
       <c r="A134" s="1" t="s">
         <v>412</v>
       </c>
@@ -6493,7 +6497,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="135" ht="86.4" hidden="1" spans="1:3">
+    <row r="135" ht="86.4" spans="1:3">
       <c r="A135" s="1" t="s">
         <v>415</v>
       </c>
@@ -6504,7 +6508,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="136" ht="100.8" hidden="1" spans="1:3">
+    <row r="136" ht="129.6" spans="1:3">
       <c r="A136" s="1" t="s">
         <v>418</v>
       </c>
@@ -6515,7 +6519,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="137" ht="100.8" hidden="1" spans="1:3">
+    <row r="137" ht="100.8" spans="1:3">
       <c r="A137" s="1" t="s">
         <v>421</v>
       </c>
@@ -6526,7 +6530,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="138" ht="129.6" hidden="1" spans="1:3">
+    <row r="138" ht="129.6" spans="1:3">
       <c r="A138" s="1" t="s">
         <v>424</v>
       </c>
@@ -6537,7 +6541,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="139" ht="72" hidden="1" spans="1:3">
+    <row r="139" ht="72" spans="1:3">
       <c r="A139" s="1" t="s">
         <v>427</v>
       </c>
@@ -6548,7 +6552,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="140" ht="57.6" hidden="1" spans="1:3">
+    <row r="140" ht="57.6" spans="1:3">
       <c r="A140" s="1" t="s">
         <v>430</v>
       </c>
@@ -6559,7 +6563,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="141" ht="86.4" hidden="1" spans="1:3">
+    <row r="141" ht="86.4" spans="1:3">
       <c r="A141" s="1" t="s">
         <v>433</v>
       </c>
@@ -6570,7 +6574,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="142" ht="43.2" hidden="1" spans="1:3">
+    <row r="142" ht="43.2" spans="1:3">
       <c r="A142" s="1" t="s">
         <v>436</v>
       </c>
@@ -6581,7 +6585,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="143" ht="57.6" hidden="1" spans="1:3">
+    <row r="143" ht="57.6" spans="1:3">
       <c r="A143" s="1" t="s">
         <v>439</v>
       </c>
@@ -6592,7 +6596,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="144" ht="57.6" hidden="1" spans="1:3">
+    <row r="144" ht="57.6" spans="1:3">
       <c r="A144" s="7" t="s">
         <v>442</v>
       </c>
@@ -6603,7 +6607,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="145" ht="100.8" hidden="1" spans="1:3">
+    <row r="145" ht="100.8" spans="1:3">
       <c r="A145" s="1" t="s">
         <v>445</v>
       </c>
@@ -6614,7 +6618,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="146" ht="57.6" hidden="1" spans="1:3">
+    <row r="146" ht="57.6" spans="1:3">
       <c r="A146" s="1" t="s">
         <v>448</v>
       </c>
@@ -6625,7 +6629,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="147" ht="178" hidden="1" customHeight="1" spans="1:3">
+    <row r="147" ht="178" customHeight="1" spans="1:3">
       <c r="A147" s="1" t="s">
         <v>451</v>
       </c>
@@ -6636,7 +6640,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="148" ht="216" hidden="1" spans="1:3">
+    <row r="148" ht="216" spans="1:3">
       <c r="A148" s="1" t="s">
         <v>454</v>
       </c>
@@ -6647,7 +6651,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="149" ht="158.4" hidden="1" spans="1:3">
+    <row r="149" ht="158.4" spans="1:3">
       <c r="A149" s="1" t="s">
         <v>457</v>
       </c>
@@ -6658,7 +6662,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="150" ht="100.8" hidden="1" spans="1:3">
+    <row r="150" ht="100.8" spans="1:3">
       <c r="A150" s="1" t="s">
         <v>460</v>
       </c>
@@ -6669,7 +6673,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="151" ht="100.8" hidden="1" spans="1:3">
+    <row r="151" ht="100.8" spans="1:3">
       <c r="A151" s="1" t="s">
         <v>463</v>
       </c>
@@ -6680,7 +6684,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="152" ht="129.6" hidden="1" spans="1:3">
+    <row r="152" ht="129.6" spans="1:3">
       <c r="A152" s="1" t="s">
         <v>466</v>
       </c>
@@ -6691,7 +6695,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="153" ht="230.4" hidden="1" spans="1:3">
+    <row r="153" ht="230.4" spans="1:3">
       <c r="A153" s="1" t="s">
         <v>469</v>
       </c>
@@ -6702,7 +6706,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="154" ht="144" hidden="1" spans="1:3">
+    <row r="154" ht="144" spans="1:3">
       <c r="A154" s="1" t="s">
         <v>472</v>
       </c>
@@ -6713,7 +6717,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="155" ht="201.6" hidden="1" spans="1:3">
+    <row r="155" ht="201.6" spans="1:3">
       <c r="A155" s="1" t="s">
         <v>475</v>
       </c>
@@ -6724,7 +6728,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="156" ht="115.2" hidden="1" spans="1:3">
+    <row r="156" ht="115.2" spans="1:3">
       <c r="A156" s="1" t="s">
         <v>478</v>
       </c>
@@ -6735,7 +6739,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="157" ht="72" hidden="1" spans="1:3">
+    <row r="157" ht="72" spans="1:3">
       <c r="A157" s="1" t="s">
         <v>481</v>
       </c>
@@ -6746,7 +6750,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="158" ht="100.8" hidden="1" spans="1:3">
+    <row r="158" ht="100.8" spans="1:3">
       <c r="A158" s="1" t="s">
         <v>484</v>
       </c>
@@ -6757,7 +6761,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="159" ht="72" hidden="1" spans="1:3">
+    <row r="159" ht="72" spans="1:3">
       <c r="A159" s="1" t="s">
         <v>487</v>
       </c>
@@ -6768,7 +6772,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="160" ht="43.2" hidden="1" spans="1:3">
+    <row r="160" ht="43.2" spans="1:3">
       <c r="A160" s="1" t="s">
         <v>490</v>
       </c>
@@ -6779,7 +6783,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="161" ht="86.4" hidden="1" spans="1:3">
+    <row r="161" ht="86.4" spans="1:3">
       <c r="A161" s="1" t="s">
         <v>493</v>
       </c>
@@ -6790,7 +6794,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="162" ht="115.2" hidden="1" spans="1:3">
+    <row r="162" ht="115.2" spans="1:3">
       <c r="A162" s="1" t="s">
         <v>496</v>
       </c>
@@ -6818,7 +6822,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="164" ht="57.6" hidden="1" spans="1:3">
+    <row r="164" ht="57.6" spans="1:3">
       <c r="A164" s="1" t="s">
         <v>504</v>
       </c>
@@ -6829,7 +6833,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="165" ht="129.6" hidden="1" spans="1:3">
+    <row r="165" ht="129.6" spans="1:3">
       <c r="A165" s="1" t="s">
         <v>507</v>
       </c>
@@ -6840,7 +6844,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="166" ht="115.2" hidden="1" spans="1:3">
+    <row r="166" ht="115.2" spans="1:3">
       <c r="A166" s="1" t="s">
         <v>510</v>
       </c>
@@ -6851,7 +6855,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="167" ht="288" hidden="1" spans="1:5">
+    <row r="167" ht="288" spans="1:5">
       <c r="A167" s="1" t="s">
         <v>513</v>
       </c>
@@ -6862,7 +6866,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="168" ht="244.8" hidden="1" spans="1:5">
+    <row r="168" ht="244.8" spans="1:5">
       <c r="A168" s="1" t="s">
         <v>516</v>
       </c>
@@ -7400,190 +7404,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E215" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Hello, Arthur&#10;Your daughter is adorable! I hope she enjoys the bunnies. I hope you reach your goal of 100 rides. I haven't ridden a bike in at least 10 years, I miss it!&#10;&#10;- Olivia"/>
-        <filter val="Hey,&#10;how is life? Mine is exciting because of a job change. Today it's runing in Wuppertal. Yesterday it was sunny and I lied at the Wupper River in Wuppertal.&#10;Have a good sunny day!"/>
-        <filter val="20 $\frac {x}{17}$ 23 +4℃ 🌥️&#10;Good day! Siyuan&#10;Warm greetings from far Lietuva. Hope You'll like both my cards and something one :)&#10;Take care&#10;Gintaras"/>
-        <filter val="Hyraa joulua ja&#10;onnellista uutta vuotta&#10;5^th^ Dec 2023&#10;Greetings from Finland!&#10;We had a christmas party today with my postcrossing friends.&#10;Had a great time!&#10;Laura/Salladeemus"/>
-        <filter val="Hello Feng. My name is Annette. Greetings from San Antonio, Texas, USA. 26 August 2024"/>
-        <filter val="Hello, I send greetings from the Baltic Sea. I'm 67, work in the garden,have 2 parrots,do crossword puzzles, meet friends for coffee and cheese cake. Best wishes, Marie"/>
-        <filter val="Namaste from India.&#10;I live in a small town Aruppukottai in South India.&#10;My town is famous for cotton mills and handloom weaving.&#10;I love collecting stamps, currencies and postcards.&#10;Wishing you lots of happiness and good health.&#10;V. Visweswaran&#10;4 May 2025"/>
-        <filter val="A card for you!&#10;I live in Rockanje, a little village near the sea and the beach.&#10;Greetings, Gerdientje"/>
-        <filter val="Hello,Feng Siyuan&#10;my name is Anja, Nice to meet you. I send you warm greetings from Pelzerhaken in Germany. Pelzerhaken is a seaside town at the baltic sea. In the summertime a lot of vacationers spend their holidays here. You want to (know) what, &quot;I love you&quot; in german is:&quot;Ich liebe dich&quot;&#10;Take care"/>
-        <filter val="Hi Siyuan Feng,&#10;If this card reaches you past 7th May:&#10;Happy Birthday to you.&#10;I hope you and your family are doing good.&#10;Your daughter looks so cute on your profile picture! ❤️ May she be blessed with health and lots of love :)&#10;With kind regards,&#10;Nicole 🌸"/>
-        <filter val="hi~你好。 Happy New Year. 好難得可以用中文來寫明信片呢！我也正在learning English喔！！！&#10;2014 1月1號 By. Yun Hung（匀虹）"/>
-        <filter val="Arthur你好。&#10;我是來自台北市的穎菲。寄上一張休閒活的一騎腳踏車的聚會片，加上一張自行車道的郵票，希望你喜歡！ :)"/>
-        <filter val="你的女兒很可愛！ 我找到這張粉紅色的貓貓postcard，閃閃的，希望她會喜歡！ 祝聖誕快樂！ 新年進步！"/>
-        <filter val="September 28,2023&#10;greetings from Socorro, New Mexico, USA.&#10;Many happy postcrossing lucks for you!&#10; Karla"/>
-        <filter val="Dearest Arthur,&#10;  Canada is now 156 years old, our flag is 58, like me.&#10;  I like to garden veggies, bake spelf bread, read, and cycle to work. Coffee and chocolate is my weakness. I work in the prison dental clinic.&#10;Wishing you much joy in your letterbox.&#10;  Linda"/>
-        <filter val="Hello from Ukraine!&#10;Here you can see the cape Tarkhankut which is situated in the south of ukraine-Crimea&#10;Hope you like it&#10;Love you: Кохаю тебе!&#10;Best regards: з найлепшымі пажаданнямі&#10;Valeriia&#10;4 march 2014"/>
-        <filter val="Feb. 9, 2024&#10;Hello Arthur and Xiaoxiao, I choose this cute rabbit for Xiaoxiao, I hope she likes it?!&#10;For your wife: I love the series:  &quot;the good doctor &quot;. Unfortunately for you I don't drink coffee...&#10;[Ik wens jou en je familie veel geluk en liefde! Groetjes van]&#10;Anne-Louise"/>
-        <filter val="hello&#10;I'm CATIA from Macao.&#10;Happy to share my artwork with you.&#10;&quot;When you start appreciating what you have, instead of lamenting what you don't have, something shifts.&quot;&#10;&#10;HAPPY POSTCROSSING&#10;CATIA&#10;8.5.2025"/>
-        <filter val="Hello Siyuan,&#10;Kind regards from the north-east of Germany. I live in a small village just by the bay between Berlin and the Baltic Sea. This tower was built as a XXX co.100 years ago to provide all houses with fresh water. Today, it is empty and became the symbol of our village. Happy postcrossing, Lupe"/>
-        <filter val="Dear Arthur, I send you and your family sunny greetings from Zadar, Croatia. I'm Jill, 21 and from Bielefeld in Germany. Your daughter is lovely! In October I'm starting to study medicine! I'm so excited. Check out the coffee from Hamburg &quot;Speicherstadt&quot;! All the best, Alles Liebe für Dich! (我祝你一切顺利！)"/>
-        <filter val="Hallo ... German Phrases! Du gehst mir auf den Keks! Literal Translation: You're walking on my cake/cookie. Meaning: You are annoying me! Happy Postcrossing. Lovely Claudine."/>
-        <filter val="23. Oct. 2024&#10;Hello Arthur,&#10;viele Grüße an Dich und Deine Familie - many greetings to you and your family. I'm Grit and I live in Leipzig, a large city in the east of Germany. I'm a doctor and work in a dialysis unit. All the best for you!"/>
-        <filter val="Feng, hello!My name is Irina, 67 y.o.&#10;I live in Podolsk, Moscow Region. I like coffee, to read, to travel around Russia. Russia, July 2025 I want to go to St. Petersburg.&#10;Best wishes!"/>
-        <filter val="hello arthur, greetings from germany. my name is michaela and I live in Fürth, a city near nuremberg. yes your daughter looks very sweet. I've a 4 y.o. son, named Lucas. I love my coffee in the morning. At the moment I've beens from india with chocolate, nougat and grapes. All the best to you &amp; your family. Michaela"/>
-        <filter val="Hello, Greetings from Poland.&#10;Have a nice time.&#10;Robert&#10;5.12.2023"/>
-        <filter val="2.10.2023&#10;Hello Arthur and Xiaoxiao!&#10;Many autumn greetings from Finland! I love the colors of autumn.&#10;Sorry I can't recommend you any coffee because I drink only tea. I love tea.&#10;I wish you all the best and stay happy!&#10;Bye, SARI"/>
-        <filter val="Hello from Russia! My name is Masha, I live in the city of Yekaterinburg. Take care :heart:"/>
-        <filter val="Hi Siyuan and adorable Xiaoxiao! Greetings from Russia! I'm 31 y.o. mom of 1.5 y.o. daughter. I work at the Russian Post office. Hope that Xiaoxiao like this gopher postcard. Wish you health and lot of joy. Tatiana."/>
-        <filter val="Hello Siyuan, Greetings from The Netherlands. My name is Willem and I live in the small village of Wezep. I send you this card from the Dutch island of Texel. It's nickname is Sheep island. I wish you all the best, Willem."/>
-        <filter val="Hello Siyuan,&#10;I'm writhing you from my town Voerendaal in the south of the netherlands. It has a population of +/- 12500 people.&#10;It is very chilly here. At the moment 3℃(12 hour) &#10;Since this week the frost set in night. Brrr…&#10;We are getting ready to celebrate Sinterklaas on December 5. IT is a fest for children. Unfortunally it was on the internatial news because some people think that his happy helpers Zwarte Piet(black Petes) and racism. Believe me, anyone who celebrate this fest for children doesn't agree to that. Maybe you heared something about it.&#10;My daughter(3) likes sinterklaas and the zwarte pieten very much. It is a beautiful tradition where we like to  kids the same as we do about Santa Claus!&#10;Groetjes  Tamara"/>
-        <filter val="Hello Siyuan, greetings from Leverkusen in the west of Germany! Today is the &quot;1st day of Christmas&quot;, but in Germany the main day of celebrating Christmas is December 24th. Funnily, it's only the 25th and the 26th that are public holidays. But as this year the 24th fell on a Sunday, everyone had 3 days off. :) Frohes neues Jahr - Happy New Yeas! Hanna"/>
-        <filter val="Hello siyuan feng and greetings from autumn Germany!&#10;I like coffee too, esp Cappuccino.There's a German Brand -Dallmayr. They were the supplier of the royal family and till now have a beautiful store in Munich. Another famous Brand is Melitta. All the best and good tastes!&#10;Victoria 28.09.2023 +24℃"/>
-        <filter val="Hello Arthur,&#10;&#10;Diese Rose ist von meiner Tochter für deine süße Tochter. Sie kommt aus einer kleinen Stadt im Süden Deutschlands. Ich wünsche dir und deiner Familie alles Gute, beste Gesundheit und jetzt viel Spaß an einer richtig tollen Rose! Love, Emily,80 years old"/>
-        <filter val="嗨！思远，你好！&#10;Apa khabar? （马来文）&#10;我是诗慧，来自马来西亚柔佛州，现在在雪兰莪州工作（车程大概3个小时）。我的祖父母从福建永春离乡背井来到马来西亚。2007年春节，我们一家陪祖母回到永春，看见到了她们那里的亲戚，也算是认祖归宗吧！明信片展示的是这里马来同袍的皮影戏。祝福你顺心如意！&#10;诗慧 SALLY&#10;16/03/24"/>
-        <filter val="Hello Arthur. My name is Iris. I live in a small town in the middle of Germany. I like going out for walks, especially in autumn in forests because of all the beautiful colors of the trees. And most times I take my camera with me. I love books and I collect cookbooks. I wish you all the best. Stay healthy and enjoy life. Warm regards, Iris."/>
-        <filter val="7.8.24 ☁️ +22°C&#10;Hello Arthur, my name is Lothar and I come from Wuppertal, a town of 360,000 inhabitants. It is situated in a green area with several dams and well known for the suspension railway and Friedrich Engels.&#10;Best wishes, HEPHAN"/>
-        <filter val="Hi,&#10;Greeting from India. My name is Ashok and I am leading a retired life in Chitradurga, a beautiful city 200 kms from Bengaluru in Karnataka.&#10;Hope this card finds you in good health and spirits. Sending you my best wishes. Stay healthy and keep smiling. &#10;Regards.&#10;Wishing you a happy new year."/>
-        <filter val="Hey, Arthur,&#10;Greetings from my weekend trip to the Sauerland and the Kahler Asten mountain.&#10;Happy Postcrossing.&#10;Kai-Jan"/>
-        <filter val="你好，我來自台灣台南的Angela，這是我寄給你的第2張明信片。挑選今年生肖&lt;蛇&gt;。第一張可能遺失了，希望你不要介意"/>
-        <filter val="&quot;Привітанне з сельскай Беларусі! ❤️ (GP Belarus!)&#10;My name's Anna. I'm 22 y.o. and I live in the heart of our Blue-eyed country Belarus — in the clean, green, and cozy city of Minsk. ❤️ Merry Christmas and Happy New Year! ❤️️"/>
-        <filter val="13-2-24 37℉&#10;Hello, Welcome back to Postcrossing! I am Mary from Massachusetts, USA. I visited H.K. a very long time ago in 1987! I enjoyed the neon and the lovely countryside,too! I hope you a safed well! XO"/>
-        <filter val="22.11.2024&#10;-3℃&#10;Hello Arthur and Xiaoxiao,&#10;Greetings from Finland!&#10;Here is a winter-time, little bit snow and sunny. I like to this time. I like to walking in the nearest forest and swimming in lake or pool.&#10;Kaikkea hyvää sinulle ja perheellesi. -&gt; All the best for you and your family!&#10;T. Paula"/>
-        <filter val="February,22nd,2024 9℃&#10;Hello, this card just means: Sleep well! I'm Anja and in wintertime I like to play boardgames with my friends and family. In spring and summer I like hiking very much. I'm sending you best wishes, Anja"/>
-        <filter val="HELLO!My name Kate. Greetings from saint-Petersburge, Russian Federation! I'm 28 years old. I have the husband and the son. We wish you a Merry Christmas and Happy New Year!"/>
-        <filter val="May 7th&#10;Dear Arthur,Here is a view of a popular place for tourists to visit in England. There are many beautiful areas to walk in e.g. woodlands where you can see wildlife. Best wishes, Laura"/>
-        <filter val="Hello Arthur! Greetings from Kyiv Ukraine!&#10;Берегите один одного та мир в країні!&#10;Take care of each other and peace in the country!&#10;Natalia"/>
-        <filter val="hello Arthur, warm greeting from southern germany. Your daughter is very cute. Does she know peppa pig. all the best, PIA"/>
-        <filter val="Jan. 20, 2025&#10;Hello Arthur, many greetings from Czechia! I am Vladimir, and I live in Prague, the capital. I send you this picture of the nice dog, which is an Assistance Dog. I support an organization, it is called Helppes - means Help dog.&#10;Best wishes for you, Vladimir"/>
-        <filter val="Hello,&#10;many greetings from Germany.&#10;I am 67, married, retired from IT --work in a bank. Best Wishes"/>
-        <filter val="Dear Arthur, &#10;I'm very glad to send you the postcard because I rarely send a card to a person also speak Chinese. I still write the card in English since I want to seize every opportunity to improve it. You must be cheerful to have a charming girlfriend. Falling in love with someone is always joyful. Hope you two in love smoothly forever. Penny 30.3.2014&#10;Happy postcrossing"/>
-        <filter val="Dear Arthur:&#10;Howdy, (Texan for hello) from the pine forests of Northeastern Texas! I'm Mike, 70 years (body only. The Mind is much younger :))&#10;Married to Lewa the past 43 mostly happy years :)&#10;Retired, we live in a small city of 23000 with Lucy our puppy :)&#10;Happy Post Crossings!"/>
-        <filter val="Happy Belated Birthday!&#10;A horse stamp and our beautiful black bears&#10;for your adorable daughter!&#10;❤️ Lisa"/>
-        <filter val="Hello from New Hampshire, USA! I'm 32 ＆ live with my husband. We are enjoying a nice, cozy weekend. Later we are meeting friends for dinner. Cleers! Blair"/>
-        <filter val="Bonjour Arthur et Bonjour XiaoXiao!&#10;Joyeux nouvel An chinois! Je vous souhaite beaucoup de chance et une bonne santé! (Happy lunar new year! I wish you a lot of luck and great health.)&#10;I am currently traveling through China and south east asia , I have been to singapore and Hong Kong and I'm currently in Taiwan! They make incredibly strong coffee!!&#10;Best, Sophie&#10;26.02.24"/>
-        <filter val="最近很累、很困，不知道怎么样才能好好休息到 T_T。&#10;YY 2024"/>
-        <filter val="hello! I hope you are doing great! I love this card, I got it in a set of 10 and it's been so difficult to send them all out. It's been 4 years since I got them :D I always make the same mistake of getting a set of cards and then struggling to send them out. You know how you don't like some of the cards in the set :D Best wishes ♡ deimante"/>
-        <filter val="Hello!&#10;Greetings from Finland! I hope maybe your daughter likes this card. Is her nickname 小小? If so, that is a very cute nickname!&#10;&#10;Here in Finland, it has started snowing.&#10;&#10;Best regards,&#10;Kuu"/>
-        <filter val="Dear Xiaoxiao,&#10;I hope that you like this card of a baby bear. Isn't it cute?&#10;Lovely greetings, Becky"/>
-        <filter val="Hello Arthur and Xiaoxiao!♡ My name is Nastya. Warm greetings from Russia! I have a son, he's 2 y.o. now. His favorite animal now is an elephant :) On the back is an inscription: &quot;the world breathes love&quot;.♡ Let your home be full of love and comfort!♡ All the best, Nastya, Voronezh, Russia."/>
-        <filter val="Hello!My name Polina, I'm 13! I very love China's cities! Happy Postcrossing."/>
-        <filter val="Hallo Siyuan Feng!&#10;SEND YOU BEST WISHES FROM MY WONDERFUL CITY INNSBRUCK/AUSTRIA EUROPA! :) THE CITY IS SURROUNDED BY LOTS OF MOUNTAINS WHICH GIVE US MANY OPPORTUNITIES FOR GREAT SPORT ADVENTURES.&#10;TAKE CARE&#10;Karin"/>
-        <filter val="May 20th, 24&#10;Hello Arthur,my name is Karin. I am 61 years old. I have been married for 35 years and we have two adult children. I hope you have fun with your little daughter. A child is special. Greetings from Aschaffenburg, Germany. I hope you like this animal card! Regards."/>
-        <filter val="Hello Siyuan feng,&#10;nice to write you my first english writing postcard.&#10;My name is Jannie, iI'm 29 years old and my hobbies are geocachen, my fishtank with south american fishes, writing my  book blog (bluebutterfly.wordpress.com). You want to learn to write&quot;I love you&quot; in Germany &quot;Ich liebe Dich&quot;&#10;With best regards to oyou and your girlfriend.  &#10;Janine"/>
-        <filter val="Hello Arthur!&#10;Greetings from Montreal!&#10;I'd like to share a saying that I try to live by:&#10;Look for something positive in each day!&#10;Even if some days you have to look a little harder."/>
-        <filter val="Hello Arthur, I am Jussi from Helsinki, Finland. I am working in the hotel industry and will retire in the end of next year. I love gardening at my country cabin, hunting mushrooms, visiting museums, eating out and travelling. My husband turns 60 on August 25th. We are going to celebrate his birthday in Torrevieja, Spain. Peace &amp; Love, Jussi."/>
-        <filter val="2025 April 24&#10;&#10;Hello Arthur!&#10;Here in Skagit Valley we host a Tulip Festival every April. People visit from all over the country and world to see them. I have also taken up cycling recently though mine is an e-bike with extra storage capacity for camping trips. I'm currently in a state of anxiety for 3 months because of Trump, who is causing a lot of disruption in the US and internationally. I hope your work is not impacted. I am a scientist and some of my colleagues are unable to do their work due to federal funding cuts. It is madness."/>
-        <filter val="Bonjour! Hello from Belgium!&#10;My name is Laurence. I live in Brussels.&#10;I love drawing as you can see on both sides.&#10;I love traveling too. We're back from a lovely spa break in Luxembourg.&#10;I wish you a wonderful 2025!&#10;Cheers!"/>
-        <filter val="Hello, this card comes from Southern Germany. The castle was built in the 19th century by a crazy king who wanted to escape into a fairy tales world. Today one of the most visited place in our country. Best wishes, Patrick 26. July 30°C"/>
-        <filter val="Chemnitz 20.1.25&#10;&#10;Hallo Arthur,&#10;We hope that you like this Postcard&#10;Have a nice day&#10;Siegfried"/>
-        <filter val="Greetings from the historical center of Moscow. I love crochet and sometimes make toys to my childrens. +1 ℃&#10;Good luck! Ledon2015. 24.02.24"/>
-        <filter val="Hello Arthur, Greetings from the USA. Your daughter is so cute. Where I live we make more RV's (travel trailers-motorhomes) than anywhere else in the world. I hope you are having a great 2024. Prayers for your health and happiness. In friendship, Valerie"/>
-        <filter val="Hi Arthur! I hope Xiao Xiao likes this card of a cat! He's stealing a fish. I recently adopted a kitten and he's very cheety too. His name is Apollo.&#10;Happy postcrossing and best wishes from the Netherlands!&#10;Femke"/>
-        <filter val="So nice to visit with you again. I hope 2023 has been good so far.&#10;&#10;My card shows 3 generations of weddingsin my family. Notice that all 3 brides are wearing the same gown. My mom in 1954, Me in 1985 and my daughter in November when she married the love of her life. It's once again set aside for the next bride, ifshe desires to follow suit&#10;&#10;Thanks for swapping and here's to a mailbox full of great cards!&#10;&#10;Arthur- I sent this Card earlier this year, and thought you might like it.&#10;your daughter is cute!&#10;Ilyse"/>
-        <filter val="Dear Feng,&#10;Happy new year!&#10;2014-sarah"/>
-        <filter val="&quot;Hi from the state of Minnesota, in north central USA.&#10;People like to spend vacation time on the shores of lakes in the north woods.&#10;This is a beautiful area. Sometimes I feel sad that 200 years ago when the land was being settled,   &#10;so much natural grassland was destroyed to plant crops.&#10;STACY"/>
-        <filter val="Hello,&#10;here's coming a postcard from little island called Föhr.&#10; It's in the north of germany. I live here along mh live. &#10;Have a nice time.&#10;Greetings Kirstin"/>
-        <filter val="Hello Arthur,&#10;how're you? My name's Tereza, I'm 20. In the picture you can see hotel,where I work like a receptionist and some landscapes. Yeah, you're in Texas right now! It's really interesting!&#10;Hope you 're enjoying summer&#10;Have a good time,Tereza."/>
-        <filter val="Dear Arthur, best regards from essen in the ruhr-area, Germany. I'm Anne, 66 years old. your daughter is really cute, she looks like a doll. I have 4 grandchildren, but they are all boys, the youngest is only 4 months old."/>
-        <filter val="Feb 10 2024&#10;HEllO FROM TORONTO&#10;XiaoXiao is so adorable, what a beautiful daughter you have. Is she as sweet as she look? I have a 29 yr old daughter and a son who wil be 34 this summer.&#10;I tell you don't blink and don't waste money on toys, expensive trps and fancy clothes they remember nothing. The time together playing is the best. I wish you all good health and much happiness.&#10;From Sandra"/>
-        <filter val="Hello Siyuan!! Greetings from Japan.&#10;I live in Yokohama, next to Tokyo.&#10;中国の漢字は難しいです。日本の小学校では1026文字も習います。&#10;When writing an address in Japan, we write '様' at the end of the name, but do we do it in China? 元気 でね!&#10;♡ Xiaoxiao かわいいね ♡&#10;Azusa&quot;"/>
-        <filter val="友友好！请查收来自中大的明信片。 我叫霜仙，是在穗厦门人，我现在在中山大学读博。寒暑假才会回去，这是我拍的厦门后田海滩，我把它做成明信片送给你。背面是我设计的。希望你喜欢。&#10;    中大今年一百周年校庆非常隆重。第三校歌《快来报中大》太燃了，还有广寒宫的歌舞也很美！欢迎友友来中大&#10;2024.11.22"/>
-        <filter val="Happy New year and Christmas!!! &#10;Lesya 10.12.2013"/>
-        <filter val="Hi Siyuan, Welcome from Winnipeg in the middle of Canada. What a cute avatar. My grandniece lives in Malaysia and is 2. I love to WhatsApp with her. She loves to sing with hand gestures! Cheers, Sandee"/>
-        <filter val="Dear Arthur,&#10;Hi, my name is Sarah and I live in the small city of Auburn in New York State. Fall is my favorite season because the countryside looks like this postcard.&#10;Happy Postcrossing! -Sarah"/>
-        <filter val="Hello from Georgia! My name is Dani and I live on a small farm in Georgia south of Atlanta. Atlanta is the home of the world's busiest airport and was the birth city of Coke-a-Cola. I hope your daughter likes the cat and horses. Peace + Smiles :)"/>
-        <filter val="eine herzliche Umarmung für deine süße Tochter&#10;(=a hearty hug for your sweet daughter)&#10;Today is word-postcard-day, you can colour this card and changes the image when you are ready.&#10;stay healthy and peace in the world.&#10;Be (Bruno)&#10;"/>
-        <filter val="Ni hao Arthur,&#10;my name is Diane. your daughter is indeed adorable.&#10;Specially for her, I send this cute card :smile:&#10;We drink Wakuli coffee beans = &quot;FAIRETRADE&quot;&#10;enjoy life :heart:"/>
-        <filter val="Hi! My name is Darina, I'm from Samara(Russian) Hope you'd like this card with the view of the Hermitage Museum in St. Petersburg&#10;Good luck and happy postcrossing."/>
-        <filter val="Hello Arthur, Warm greetings from Australia on this late autumn day. &#10;I thought this funny postcard with the cycling kangaroo would satisfy you and your daughter. &#10;I'm sure you could pedal faster. &#10;&#10;Best wishes, &#10;John"/>
-        <filter val="Hello siyuan!&#10;Greetings from sw Florida in USA! We visit this zoo often and see Walter! He is so handsome! I live 7 miles from the ocean, and we get the most gorgeous sunsets! We also have sea turtle nesting season here. All nests are protected. I wish for more and less hate in the world."/>
-        <filter val="February 10, 2024&#10;Moi,Hello Arthur!&#10;greetings from Finland!&#10;My name is Emmi, I live in the western part of Finland in a city called Tampere. It's located between two beautiful lakes. It is said Finland is the land of a thousand lakes - we have so many of them! :)&#10;Happy postcrossing!"/>
-        <filter val="18.01.25&#10;-2°C&#10;Dear Arthur,&#10;I send you a lot of greetings from Germany. I'm living with my family in the near of Hamburg. We love it to travel. :) Best wishes &amp; a lot of fun with post-crossing.&#10;Andrea"/>
-        <filter val="Dreumel, 17-10-2023&#10;Hello Arthur,&#10;My name is Esther and I live in avery small village with my man and our dog and cat. l do like alot. like reading, writing, Escape rooms, traveling and baking sweet treats, mainly cup cakes.(Insta:Essies_cupcakes).&#10;ik hoop dat jij deze kaart leuk vindt. Ik doe dit (diamond painting) als ic myn hoofd leeg wil maken. Ik werk full time in de IT sector als applicatie consultant. so l hope it make sense if you try to translate it. I wish you a nice day and of course Happy Postcrossing.&#10;kind regards,&#10;Esther"/>
-        <filter val="My name is Holger. I'm a teacher of mathematics and ethics, married, father of two sons. We live in a 172 years old house with our own library.&#10;Best Wishes! &#10;Herzlich Grüße! Holger"/>
-        <filter val="Arthur!&#10;&#10;Greetings from Russia! I live in Moscow. Today - 5 degrees. I'm looking forward to spring. I'm sending this bird to your little daughter. I wish you health and smiles. Happy postcrossing.&#10;И самые лучшие пожелания вашей семье. :)&#10;&#10;Yulia&#10;21.02.24"/>
-        <filter val="Hei&#10;17th of Juney 2024&#10;Greeting from sunny Finland. Now at 8.30 am is 20° C. Sun has arisen at 3.37 am and will go down at 10.50 pm.&#10;I’m a biology, geography, and social studies teacher (also math this school year) in upper comprehensive school for pupils with 13-16 years old. I like my job very much.&#10;I have MCTD. It’s rare of rheumatism disease. I have so much pain in articulations that handwriting isn’t possible. June 2023, I got another rheumatism diagnoses, psoriatic arthritis.&#10;I try to be positive. I have personal assistant who help me with Postcrossing and many other things.&#10;On school time I got to work by taxi because public transport isn’t going near to school (I should walk from bus stop about a one km). At school I’m not allowed to walk stairs alone, my classroom is at 3rd floor and in my school isn’t lift/elevator.&#10;I want to go work because when I’m teaching, I don’t think about pain. I have use wheelchair in my free time.&#10;Our school year ended at 1st of June and back to schools we go at mid-August.&#10;Anne (veverka)"/>
-        <filter val="Dear Feng,&#10;I love all the national parks in the US and California has the most.&#10;Sending you best wishes from La La Land.&#10;Cheers!&#10;Cardiffgal"/>
-        <filter val="Big hello from Moscow, I just got here from my trip to Rwanda and Egypt, bought this postcard in a local store in Cairo. I think it is cute and also has cool lenticular eyes. My niece turned 1 y.o. three weeks ago. Time passes by so quickly but that's okay. It is part of life."/>
-        <filter val="Hi Feng Siyuan, My name is Natalia. I live in a small Ural town. I really want you to get my postcard. And it will bring you joy and a smile. You have a very beautiful daughter. May your family live in love and harmony. Всего вам самого доброго С любовью из России!!! от Натальи&#10;&#10;Не знаю сколько будет в пути это письмо, хочу поздравить вашу семью с наступающим Новым годом 2025!!!&#10;Пусть новогодняя ночь будет волшебной и принесёт много подарков.&#10;Наталья"/>
-        <filter val="Hello Feng,&#10;my name is Leila and I am thrilled to introduce you to Bosnia, an ex-Yugoslavian country in the heart of the Balkans.&#10;&#10;I'll start with &quot;Ćejf&quot;, a concept about savoring the moment, like enjoying a cup of coffee or a conversation with a friend, taking time to relax is a cherished tradition here.&#10;&#10;Jufat - a Bosnian treat, a kind of stubborn pride or defiance. It helped Bosnians persevere through challenging times.&#10;&#10;Deret - it conveys a deep sense of sorrow and heartache, it reflects pain, but also embodies the idea of enduring and sharing one's burden with others.     &#10;&#10;Veliki pozdrav iz Sarajeva"/>
-        <filter val="25.1.25.5&#10;Hello to the world from the Town Sprockhodel in Germany. I hope you like the posthaute... you see the olympic games in Paris in 2024. I ❤ this postcard.&#10;I live in a nice house on the edge from fields and woods with my little family. Every day I go with my Dog Elli ou little adventures... I wish you all the best and in the year 2025!"/>
-        <filter val="Прывітанне з Беларусі!!! My name is Dima. I live in the city of Volkovysk near the border with Poland. I'm 48 years old. I like rock music and travel. Прыветная посткроссинг!!!"/>
-        <filter val="2.13.24 SUNNY 62 ℉&#10;HELLO ARTHUR AND XIAOXIAO, I HOPE YOU BOTH LIKE THIS CARD. IT WAS MADE BY A LOCAL ARTIST. I LIVE IN NORTHERN CALIFORNIA, NEAR SACRAMENTO, WHITCH IS THE CAPITAL. I TOOK A 10 YEAR BREAK FROM POSTCROSSING :smile:&#10;LOCAL COFFEE - TEMPLE, PHILZ AND THE MIU &#10;-TRISH"/>
-        <filter val="Hello Arthur!&#10;GREETINGS FROM COLLEEN CRAFTYHILL&#10;a Canadian living in Speyer, Germany on the Rhine at Km 400.6.&#10;&#10;The Rhine is low at 2.80 m but it is up from 2.19 m at which much of Rhine transport was halted.&#10;I wish you all the best with your goal of 100 100 km road races. Very cool!!&#10;&#10;Your daughter is very cute indeed. My &quot;fur baby,&quot; Dante, is quite cute, too.&#10;I'm a tourist guide here in Speyer. I love my job!&#10;&#10;All the best,&#10;Colleen"/>
-        <filter val="Hello, Arthur!&#10;I live in the city Gomel - the second largest city in Belarus.&#10;I was a teacher. Now I am retired.&#10;I like to read,to travel.&#10;I congratulate you and your family( your  daughter is adorable,with new year.and may all your dreams come true! Galina"/>
-        <filter val="Hi! from San Diego California! This card is from our favorite local coffee roaster. Just a short walk from our house— Happy Postcrossing! Many love &amp; greetings"/>
-        <filter val="Greetings from Luxembourg!&#10;Originally I am from Russia but I have lived in this small green and calm country for 3 years.&#10;I think this postcard will arrive after 7th May, but I still want to wish you all the best&#10;wherever you are and whatever you do—I hope you enjoy life and have fun! 😊&#10;&#10;Warm hugs from Luxembourg!&#10;Daria&#10;24.04.25"/>
-        <filter val="9.2.2024 -22℃&#10;Hello.&#10;[talviset terveiset ta alta lumisesta suomesta] = Winter greetings from here snowy Finland. At this moment snow level is about 80 cm. But still 2 months time rain more. Then it's start melt away. I hope Best wishes, JARI"/>
-        <filter val="Hello Arthur,&#10;I'm Günter, live in Rödermark and are retired.&#10;I have a garden,like to travel, play bowling&#10;best wishes and stay healthy"/>
-        <filter val="Hello Arthur,&#10;many greetings from Schorndorf,&#10;in the south of Germany. My name is Gabi and I like: musicals, movies,books long walks in the nature, animals, time with my friends, traveling, writing letters of postcards and sport.&#10;I wish you all the best for 2024.&#10;Gabi"/>
-        <filter val="Dear Arthur,&#10;Belgium is great for cycling (very flat), but this view is paradoxically from a hill. Mont des Arts is a part of Brussels with many museums and historical buildings.        &#10;Happy 2025 and happy pedalling!&#10;Michael"/>
-        <filter val="Hi,Arthur! 13.11.2023 22:20&#10;My name's Diana. I live with my beloved husband in a small town called Temruk. It's situated on the coast of the  Azov Sea. (Look at the map you'll see me!) I really enjoy my life here in this region. There's one more sea not far from here-- The Black Sea. I love it so much. I'm a great sea lover and can't imagine my life without that raise of sea waves. It really heals my soul and my body. Art and music also make me happy and my live with love. My favourite band is the Beatles. As all times! But there're more other bands I love. My fav. artist is van Gogh. I'm so into his piece of art. hope you'll like this cute picture and ginger cat on it.&#10;Ginger cats are my favourite one."/>
-        <filter val="New York City&#10;May 13, 2024&#10;Hello Arthur—&#10;Here are some books I’ve recently enjoyed: HHhH by Laurent Binet; A Gentleman &#10;in Moscow by Amor Towles; &#10;A Few Right Thinking Men by Sulari Gentillu; Six Four by Hideo Yokoyama; &#10;Small Mercies by Dennis Lehane; &#10;A Rising Man by Abir Mukherjee.&#10;Best, Jonathan"/>
-        <filter val="To: Siyuan&#10; Nice to meet you, I sent you this card is has reason. This postcard means we must treasure the time. Don't waste the one week without doing anything. Time is valuable. I hope you can understand the meaning of the postcard and do it in your every day life.&#10;Beside that, I have a request. Can you send me a postcard? I am very instersted about the postcard in China. Thank you.&#10;From:kaiQin"/>
-        <filter val="Dear Arthur,  01.10.2023&#10;My name is Birgit and I live in Linz, which is located in the north of Austria. It's a bigger city than salzburg, but definitely not that famous.&#10; I love reading books, traveling the world, archery, writting letters in the old style (pen and paper) and doing handicraft. Wish you all the best,Birgit."/>
-        <filter val="23.4.2014  +8℃&#10;Greetings from Pöytyä, south-west Findland! I like all kind of outdoor activities, enjoy hiking and cross-country skiing very much. Orienteering sport is my favorite hobby. I love to run in the forest with the map and compass and try to find control points quickly. I wish all the best to you and your girlfriend. I love you is : Minä rakastan sinua in Finnish."/>
-        <filter val="Hello,siyuan&#10;I'm from the northern part of The Netherlands.&#10;you want to know how you say &quot;I love you&quot; in our language--In dutch you say:&quot;IK hou van jou&quot;&#10;Blessings for you and your family.Happy postcrossing. Most kindest regards. &#10;Hugo"/>
-        <filter val="Monday October 21, 2024&#10;Arthur and Xiaoxiao,&#10;Greetings from south west Wisconsin, USA.&#10;We are enjoying warm days although it is Autumn. The leaves are changing color.        &#10;Merlin AKA xenop"/>
-        <filter val="Hello Arthur,&#10;&#10;I hope you and your daughter like the card.&#10;Good luck with your bike riding.&#10;Happy Birthday!&#10;God Bless,&#10;Diana"/>
-        <filter val="Hello,Arthur,&#10;Greetings from Moscow, Russia. My name is Alexander. I'm a metrotrain driver. I want to wish you to stay safe, to keep healthy and be happy!!!"/>
-        <filter val="Hello Arthur, I’m 18 y.o Ivanka from Ukraine. I’m sending this postcard from the capital of neighbouring Poland which hosted many ukrainians who fled the war unleashed by Russia. My family is also scatted around Europe, and most of my dreams has been decimated. I study biotechnology but it was pretty much complicated to work at the lab under Russian missle attacks. Yours perhaps is the longest address I ever wrote at postcrossing. Cheers, Ivanka"/>
-        <filter val="Hello Arthun and Xiaoxiao! My name is Yulia. I live in Istra(Moscow region). &#10;Привет из России&#10;23.10.24"/>
-        <filter val="Hi Arthur! I am Jaime from Bilbao, North Spain. I selected this card thinking about your nice boy Xiaoxiao. Hope you enjoy. All the best for your great family, Jaime"/>
-        <filter val="Hello. Three things about me! &#10;#1- I voted for Kamala&#10;#2- I am 50 years old &#10;#3- I ❤ Diet Coke"/>
-        <filter val="Original Text:&#10; November 3, 2024&#10;Hello Arthur and Xiaoxiao and mama!&#10;Greetings from Washington State USA.&#10;I think this card is very cute, I hope you like it! Best wishes to you! 😊&#10;☮Archelle"/>
-        <filter val="Hello, Arthur! Greetings from Russia. I live in Moscow, but recently I spend my holidays in Crimea, in Sevastopol (Black Sea, Russia)—it's a beautiful place. Welcome to Russia! Russia is grateful to China for the support in this difficult time. Best wishes, Andrey"/>
-        <filter val="12/02/2024 8℃&#10;AHOJ ARTHUR!&#10;GREETINGS FROM THE UK!&#10;I PICKED THIS POSTCARD BECAUSE IT MATCHED CUTE BABIES(AS YOUR DAUGHTER, SHE'S ADORABLE!) AND ANIMALS :heart:&#10;I CAN'T REALLY RECOMMEND ANY COFFEE BEANS BUT HOPE YOU'LL FIND SOMETHING YOU'LL :heart:&#10;TAKE CARE, PATRICIA :smile:"/>
-        <filter val="Hello Siyuan, My name is Frank I send you greetings  and best wishes from Germany.Frank"/>
-        <filter val="Arthur, hello from the mountains of North Carolina &#10;This is along the Appalachian trail, the longest hiking-only trail in the world.&#10;It runs for 3524 km through 14 states.&#10;&#10;Best Wishes&#10;Jim"/>
-        <filter val="Stamp Out Boring Mail!&#10;14 march 2024&#10;Hello from Minnesota. We are called &quot;The Land of 10000 Lakes&quot; and &quot;The North Star State&quot;. &#10;Your daughter is super cute!&#10;I've lived here most of my life, but also in other states. I like it here but winters are cold.&#10;Wishing you and your family health and joy, Melissa."/>
-        <filter val="Hi！&#10;Hello from across the world.I'm Gelinda, nice to meet you.Your card is the first one in a really long time, so Happy Postcrossing and hope you have a nice day. I'll. I live in a small country named Latvia, it's small, but have a nice nature."/>
-        <filter val="Hello Feng,&#10;I am Vidhya from India I live in USA now. How is Xiao?&#10;She is cute. Have you tried any Indian cuisines?&#10;Have a great day."/>
-        <filter val="Nihao Feng, Siyuan&#10;&#10;Traveled to China in 2006 for 4 weeks, learned a few words of Chinese while I was there, loved Guilin and the Great Wall.&#10;&#10;Greetings,&#10;Maria"/>
-        <filter val="DECEMBER 4 2023&#10;Hello SIYUAN.&#10;It's currently 2:00 PM. Here In White  Deer TX. The wind is blowing and the temperature is perfect. It's 70℉ definitely not normal for this time of year. measurable snow, just a bit of rain and ice. This usually means ice storms come Jauary. Have a wonderful day. take care --Nicole"/>
-        <filter val="Hi,&#10;Greetings from the north west of France. I hope you 'll like this card. Happy postcrossing.&#10;Aline"/>
-        <filter val="Hello!&#10;my name is Julia. I am from Kyiv, Ukraine.&#10;18.01.2025"/>
-        <filter val="Dia dhuit meaning hello in Irish, or, it's literal translation is 'God be with you'. My name is Zoe from Ireland; I was born &amp; bred here. I love animals and work as a veterinary nurse in Dublin. And I just got married 2 weeks ago at the 'Cliffs of Moher'. Best wishes, Zoe :)"/>
-        <filter val="Greetings from Las Vegas! We are currently in the middle of our spring, which is my favorite season before we have our desert summer heat! -Demian"/>
-        <filter val="你好 こんにちは！我是博子。來自日本的問候。這張明信片描繪了自1624年左右開始舉辦的節慶。如果你喜歡的話我會很高興。祝你天天快樂。博子"/>
-        <filter val="Hello Arthur,My name is Lutz.&#10;I live in Berlin, the capital of Germany.&#10;I'm a 65 years old single.&#10;I love it to be naked on the beach or at other places in nature, but the last summer is long over.&#10;Now I'm waiting for the next.&#10;Happy postcrossing and a good time to you!"/>
-        <filter val="January 18, 2025&#10;Hello Arthur!&#10;Greetings from San Diego. Good luck with your cycling goal! It's great to set up goals like these to keep the motivation up. I'm not a sporty person, but I'm trying to increase my activity this year.&#10;Wish you all the best!&#10;Martina"/>
-        <filter val="7 May 2024&#10;Bengaluru &#10;Dear, Feng Siyuan &#10;Namaskara from Karnataka India, I'm thrilled to share with you a unique aspect of our cultural heritage Bhuta kola, a traditional folk dance form that's an integral Part of our state's rich traditions. &#10;Bhuta kola is a vibrant and energetic dance form that's performed to appease the spirits and ancestors. The dancers, adorned in elaborate costumes and masks, enact mythological stories and legends, accompanied by rhythmic drumbeats and music. This ancient art form is a testament to our state's cultural diversity and rich history.&#10;Thank you!"/>
-        <filter val="October 21, 2024&#10;Hello Arthur!&#10;My name is Jutta. I live in Vienna, Austria, Europe, in an apartment with a small balcony. There I often get visits from nice birds, butterflies, bees, bats, and cute squirrels. Ich wünsche Dir und Deiner Familie Freude und Gesundheit.&#10;Viele liebe Grüße,&#10;Jutta"/>
-        <filter val="7th July 2024&#10;Hi Feng!&#10;My name is Paula and hometown Lahti. We have one dog called Roxy. He is a basenji 13 years old. He is at home with my husband ’cause I’m with our daughter at her cottage with two of her dogs.&#10;All the best to you!&#10;Paula"/>
-        <filter val="Hello Arthur, I'm Christiane and I live in a suburb of Berlin. I also really enjoy cycling. I travel by bike, meaning I carry all my luggage on my bike. I really enjoy it. Sometimes a trip can be 100 km long, even though I only plan for about 80-90 km. A day trip can sometimes be 120 km long. I think we have a great hobby.&#10;In winter, I plan my trips, I read books with historical background and write postcards. I wish you and yours all the best! And always enough air in the tires!&#10;Kind regards, Christiane&quot;"/>
-        <filter val="こんにちは！（konnichiwa, hello） My name is 和永（Kazue） I live in 奈良（Naha）, Japan. Nara「～～」1185, the old city where there was the capital called 平城京（Heijo-kyo）about 1300 years ago. This is 祇園祭（the Gion Festival in Kyoto），which takes place every July. Happy postcrossing! 2024.10.23"/>
-        <filter val="Dear Arthur,This postcard comes to you from Northern Germany. I love books and sports and I am a volunteer with the Red Cross. That's fun! Best regards from Europe,INGE"/>
-        <filter val="March 01, 2024, 7°C,rainy&#10;Hello Arthur and your family,&#10;I'm delighted to be sending you a postcard. I'm Lara and I'm from Stuttgart, Germany. Today is my friend's birthday He's turning 41.&#10;However, he doesn't enjoy celebrating his birthday much, so we're working as usual today and will go out for dinner after work My friend is from South Korea, and we both love Korean food Normally, we enjoy cooking ourselves, but in the past few months, many Korean restaurants have opened here, and some of them are quite good.&#10;Last year, we also spent a month in South Korea with his family. It was one of the best trips I've ever taken. I learned so much about the culture and life there, as we stayed with his family, of course. I'm already looking forward to the next time we visit his family.&#10;[Redet mit jedem Menschen freundlich: alles, was ihr sagt, soll mit Salz gewürzt sein. Bemüht euch darum, für jeden die richtigen Worte zu finden.]&#10;At the front of the card in German it says:&#10;Speak kindly to everyone, everything you say should be seasoned with salt. Endeavor to find the right words for each"/>
-        <filter val="Greetings from Boston! We have visited Beijing and loved it. I hope Xiaoxiao enjoys the Sesame Street stamps. Warm Wishes,&#10;Sarah"/>
-        <filter val="Hello from hot and sunny New Mexico, USA. I like living in the American Southwest. We moved from Arizona, where this animal park is located. It's fantastic! It is also near the Grand Canyon, which I have seen several times. We're going on holiday to Canada in October. GARCI"/>
-        <filter val="P1：&#10;Hello From France&#10;You who love sports&#10;I found a card (sliding sports) and a surprise for your daughter.&#10;I'm writing to you in French my first name and where I'm writing from.&#10;&#10;je m'appelle CHANTAL&#10;je vis sur la côte Atlantique dans le Sud-ouest de la France. Bisous. - Chantal&#10;&#10;P2:&#10;A little surprise For you, my little love. You are very pretty. I send you Big hugs. :) CHANTAL"/>
-        <filter val="OSTRAVA!!&#10;Lower Vitkovice is a national site of industrial heritage located in the Vitkovice district of Ostrava in the Czech Republic. it includes an extensive industrial area Vitkovice ironworks with a unique collection of industrial architecture. A set of threesuccessive parts - coal mine, coke ovens and blast fumnace operations - also called Ostrava Ostrava Hradcany, after Hradcanythe Castle District of Prague.&#10;The area is registered in the list of European cultural heritage, and was placed on the Czech Republic's list of tentative UNESCO World Heritage Sites in 2001 under the name The Industrial Complexes at Ostrava.&#10;&#10;Hi, I am Jitka from Ostrava, which is the third largest city in the Czech Republic. Have a nice day."/>
-        <filter val="Hello Arthur,&#10;Greetings from Malaysia! My name is Sookfun. I like to collect stamped and written postcards. My goal is to collect at least a card from every country in the world. Stay safe. Take care.&#10;21 May 2025."/>
-        <filter val="Much greetings from Germany.&#10;My name is Jana and I live in Cottbus.&#10;&#10;Have a great day,&#10;Jana"/>
-        <filter val="04.10.23 +17℃&#10;Greetings, from Russia! &#10;Hi, I'm Mila. I live in moscow region, in the small city with my family!&#10;I wish you all the best!!!"/>
-        <filter val="Hello!&#10;My name is Minna and I live in small town called Kauhajoki. There is about 13000 inhabitants, but I like live here.&#10;I like reading and listening to music. Also I collect stamps and Garfield and cow-cards. I like animals very much, especially cats.&#10;Happy postcrossing! Minna"/>
-        <filter val="Hello Arthur,&#10;greetings from Hamburg, in north Germany! I am drinking coffee right now, the brand is called Jacobs. It's autumn here, so I hope your daughter will enjoy this autumn forest and that you all have a good day!&#10;Best wishes, Ricarda"/>
-        <filter val="Hello arthurfsy,&#10;My name is Eiichi (栄一). I live in Tokyo, Japan.&#10;I have retired. Now, I enjoy collecting world postage stamps and walking as a daily routine.&#10;I send a photo postcard of Hokkaido Squirrel (エゾリス).&#10;Please take care and enjoy your favorite.&#10;Happy Postcrossing!"/>
-        <filter val="Stockholm 20240808&#10;Hi Siyuan(SE 237946)&#10;Hi ! (hedgehog turn around)&#10;Quite a long address, Now I copy it in Chinese.&#10;Never been to China, But I should like to go&#10;Greetings&#10;Gunnar"/>
-        <filter val="Hi Arthur! I'm Matt from Arizona. I love coffee. My favorite coffee is from Philz, a company in California. Best wishes! Matt"/>
-        <filter val="Hello Arthur,&#10;Postcards are a beautiful way to connect people and cultures. I find it fascinating how Luxembourg and China have built a strong relationship over the years, especially in trade and culture. Here in Luxembourg, we have a vibrant Chinese restaurant scene, and we love enjoying Chinese cuisine!&#10;I truly believe we should leave a better world for our children, and it's inspiring to see how Postcrossing fosters these connections.&#10;I hope this postcard brings a smile to you and Xiaoxiao! 😊   &#10;Best wishes,&#10;Laurent"/>
-        <filter val="In the fall - this is pretty much what Nebraska looks like :). Be well - Charlene"/>
-        <filter val="5^th^ Dec 2023&#10;Hello Arthur,&#10;These are scenes in the north of England. &#10;I grew up near here.&#10;Best wishes, Gordon"/>
-        <filter val="Hi,Siyuan,&#10;hope you enjoy this card. I thought it was nice to send you a heart shaped card because you are in love. I love you in Dutch is &quot;IK hou van jou&quot; Wish you all the best! On the front you see the famous Dutch coastline."/>
-        <filter val="14, February 2024 &#10;Many greetings from Almuth in Lower Saxony. I live in a small town called Quakenbrück, with a frog symbol, Already founded in 1235.&#10;Best wishes to your daughter too."/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="2024/09/30&#10;Hello&#10;&#10;hope you are fine?&#10;Wanted to ask if you have received my card BA-14379&#10;&#10;KR&#10;Leila&#10;&#10;2024/10/03&#10;Dear&#10;&#10;I am sorry, I did not take a picture, I usually do it, so I don't remember when exactly I have sent it.&#10;We will wait, hopefully it will arrive soon. The ones sent to India got there, so fingers crossed.&#10;Please just let me know.&#10;&#10;Kind Regards&#10;Leila"/>
-        <filter val="2024/10/21&#10;Wait, I sent it in an envelope&#10;&#10;2024/10/21&#10;Привет, мне выпала возможность отправить тебе открытку, можно мне отправить тебе в конверте?&#10;&#10;2024/12/11&#10;I am very glad that the envelope got to you. I wish you all the best. Have a nice day and a huge hello to your family. Be happy!!!"/>
-        <filter val="You are welcome,Siyuan.I am so happy that you can understand the meaning of the postcard!"/>
-        <filter val="Thank you for your message. Yes, that's right. Kanji is difficult, but English is difficult too. Sorry for writing in Japanese. I always use Google Translate. Take care. Happy Postcrossing. Azusa"/>
-        <filter val="Hello Siyuan,&#10;&#10;I have sent today a postcard to you.&#10;I hope it arrives quickly, it must cross a long distance.&#10;&#10;Most kindest regards,&#10;&#10;Hugo Pereira&#10;Hegedykje nr. 5&#10;9218 RC Opeinde (Friesland)&#10;The Netherlands&#10;&#10;NL-2441827"/>
-        <filter val="“Hello! I'm glad you liked the card and stamps. Yes, some of the stamps that I use are very old. Some are more than 50 or 60 years old, and some 1-cent stamps that I use are even more than 100 years old! Our postal service allows us to keep using them. I had never heard of the Tomb Sweeping holiday, so I looked it up online and read about it. It sounds like a wonderful way to honor lost loved ones and ancestors. I hope you found it peaceful and heart-filling. Sending best wishes on a sunny Saturday in Minnesota! Melissa”"/>
-        <filter val="“Thank you very much for the reference to https://www.bgi.com/.  I read the site with great interest, looking into genomics and bioinfirmatics as branches of the science I am majoing in. Take care!”"/>
-        <filter val="2024/7/11&#10;Hello Siyian,&#10;Good to hear that you liked the card.&#10;I was in US when I wrote the card and have now come to India where I posted it.&#10;Hence you find Indian stamps."/>
-      </filters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
